--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -35,31 +35,31 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00059669"/>
+      <color rgb="001A7A5E"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="002B5EA8"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00D97706"/>
+      <color rgb="009A6011"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00DC2626"/>
+      <color rgb="00A83232"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0094A3B8"/>
+      <color rgb="008896A8"/>
       <sz val="11"/>
     </font>
     <font>
@@ -103,7 +103,7 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="0094A3B8"/>
+      <color rgb="008896A8"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -190,7 +190,7 @@
         <color rgb="00E2E8F0"/>
       </right>
       <top style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="008896A8"/>
       </top>
       <bottom style="thin">
         <color rgb="00E2E8F0"/>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -386,9 +386,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4793,10 +4790,8 @@
       <c r="AE27" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="AF27" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF27" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="AG27" s="52" t="n">
         <v>2</v>
@@ -4818,13 +4813,13 @@
         <v>3</v>
       </c>
       <c r="AL27" s="51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM27" s="44" t="n">
         <v>9</v>
       </c>
       <c r="AN27" s="45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -5307,10 +5302,8 @@
       <c r="AE30" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="AF30" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF30" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG30" s="43" t="inlineStr">
         <is>
@@ -5331,22 +5324,22 @@
         </is>
       </c>
       <c r="AK30" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL30" s="59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM30" s="44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN30" s="45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="46" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Mary Judith Arias Tapia</t>
         </is>
       </c>
       <c r="B31" s="47" t="inlineStr">
@@ -5356,21 +5349,19 @@
       </c>
       <c r="C31" s="47" t="inlineStr">
         <is>
-          <t>57024211000</t>
+          <t>57219403758</t>
         </is>
       </c>
       <c r="D31" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F31" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="G31" s="48" t="inlineStr">
         <is>
@@ -5382,16 +5373,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I31" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="J31" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L31" s="48" t="inlineStr">
         <is>
@@ -5403,29 +5394,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N31" s="53" t="n">
-        <v>1</v>
+      <c r="N31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O31" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P31" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" s="51" t="n">
-        <v>2</v>
+      <c r="P31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R31" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S31" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="T31" s="48" t="inlineStr">
         <is>
@@ -5442,23 +5437,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z31" s="52" t="n">
-        <v>2</v>
+      <c r="W31" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA31" s="48" t="inlineStr">
         <is>
@@ -5476,13 +5467,13 @@
         </is>
       </c>
       <c r="AD31" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE31" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF31" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG31" s="48" t="inlineStr">
         <is>
@@ -5504,25 +5495,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK31" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="AL31" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM31" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN31" s="45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>Deyler Rafael Castilla Caballero</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
@@ -5532,7 +5521,7 @@
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>57903699900</t>
+          <t>57024211000</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
@@ -5558,16 +5547,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="36" t="n">
-        <v>1</v>
+      <c r="I32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J32" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K32" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="L32" s="38" t="inlineStr">
         <is>
@@ -5579,25 +5568,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N32" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N32" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O32" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P32" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q32" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P32" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="R32" s="39" t="inlineStr">
         <is>
@@ -5634,13 +5617,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y32" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Y32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z32" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="AA32" s="40" t="inlineStr">
         <is>
@@ -5658,16 +5641,18 @@
         </is>
       </c>
       <c r="AD32" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE32" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF32" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="AG32" s="28" t="n">
-        <v>1</v>
+      <c r="AG32" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH32" s="43" t="inlineStr">
         <is>
@@ -5684,23 +5669,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK32" s="45" t="n">
-        <v>2</v>
+      <c r="AK32" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AL32" s="59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM32" s="44" t="n">
         <v>4</v>
       </c>
       <c r="AN32" s="45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="B33" s="47" t="inlineStr">
@@ -5710,11 +5697,11 @@
       </c>
       <c r="C33" s="47" t="inlineStr">
         <is>
-          <t>57210822856</t>
+          <t>57903699900</t>
         </is>
       </c>
       <c r="D33" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
@@ -5726,8 +5713,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="53" t="n">
-        <v>1</v>
+      <c r="G33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H33" s="48" t="inlineStr">
         <is>
@@ -5735,18 +5724,20 @@
         </is>
       </c>
       <c r="I33" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L33" s="52" t="n">
-        <v>1</v>
+      <c r="L33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M33" s="48" t="inlineStr">
         <is>
@@ -5763,11 +5754,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P33" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="51" t="n">
-        <v>7</v>
+      <c r="P33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R33" s="48" t="inlineStr">
         <is>
@@ -5784,8 +5779,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U33" s="53" t="n">
-        <v>2</v>
+      <c r="U33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V33" s="48" t="inlineStr">
         <is>
@@ -5797,24 +5794,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X33" s="51" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y33" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="Z33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AA33" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB33" s="53" t="n">
-        <v>3</v>
+      <c r="AA33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC33" s="48" t="inlineStr">
         <is>
@@ -5825,50 +5826,46 @@
         <v>1</v>
       </c>
       <c r="AE33" s="51" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AF33" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AH33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AI33" s="53" t="n">
-        <v>1</v>
+      <c r="AI33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AJ33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK33" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="AL33" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM33" s="44" t="n">
         <v>4</v>
       </c>
       <c r="AN33" s="45" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="33" t="inlineStr">
         <is>
-          <t>Mary Judith Arias Tapia</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="B34" s="34" t="inlineStr">
@@ -5878,7 +5875,7 @@
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>57219403758</t>
+          <t>57210822856</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
@@ -5889,13 +5886,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F34" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="H34" s="35" t="inlineStr">
         <is>
@@ -5906,90 +5903,84 @@
         <v>2</v>
       </c>
       <c r="J34" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O34" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="R34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X34" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA34" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R34" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S34" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T34" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U34" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V34" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W34" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA34" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB34" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="AC34" s="40" t="inlineStr">
         <is>
           <t>—</t>
@@ -5999,10 +5990,12 @@
         <v>1</v>
       </c>
       <c r="AE34" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="27" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="AF34" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG34" s="43" t="inlineStr">
         <is>
@@ -6014,10 +6007,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI34" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI34" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="AJ34" s="43" t="inlineStr">
         <is>
@@ -6036,7 +6027,7 @@
         <v>4</v>
       </c>
       <c r="AN34" s="45" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -6766,7 +6757,7 @@
     <row r="39">
       <c r="A39" s="46" t="inlineStr">
         <is>
-          <t>Jenifer Yoris Vasquez Aguilar</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="B39" s="47" t="inlineStr">
@@ -6776,7 +6767,7 @@
       </c>
       <c r="C39" s="47" t="inlineStr">
         <is>
-          <t>57205400052</t>
+          <t>57804909800</t>
         </is>
       </c>
       <c r="D39" s="48" t="inlineStr">
@@ -6844,8 +6835,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q39" s="51" t="n">
-        <v>4</v>
+      <c r="Q39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R39" s="48" t="inlineStr">
         <is>
@@ -6877,16 +6870,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X39" s="51" t="n">
-        <v>2</v>
+      <c r="X39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y39" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z39" s="52" t="n">
-        <v>1</v>
+      <c r="Z39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA39" s="48" t="inlineStr">
         <is>
@@ -6903,52 +6900,52 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD39" s="50" t="n">
-        <v>1</v>
+      <c r="AD39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE39" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ39" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL39" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN39" s="45" t="n">
         <v>3</v>
-      </c>
-      <c r="AF39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG39" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK39" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL39" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM39" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN39" s="45" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
@@ -6958,7 +6955,7 @@
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>57804909800</t>
+          <t>57197028938</t>
         </is>
       </c>
       <c r="D40" s="35" t="inlineStr">
@@ -7066,10 +7063,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y40" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Y40" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="Z40" s="40" t="inlineStr">
         <is>
@@ -7091,10 +7086,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD40" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD40" s="41" t="n">
+        <v>1</v>
       </c>
       <c r="AE40" s="42" t="n">
         <v>1</v>
@@ -7117,26 +7110,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AJ40" s="63" t="n">
-        <v>1</v>
+      <c r="AJ40" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AK40" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL40" s="59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM40" s="44" t="n">
         <v>2</v>
       </c>
       <c r="AN40" s="45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="46" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="B41" s="47" t="inlineStr">
@@ -7146,7 +7141,7 @@
       </c>
       <c r="C41" s="47" t="inlineStr">
         <is>
-          <t>57197028938</t>
+          <t>57215550013</t>
         </is>
       </c>
       <c r="D41" s="48" t="inlineStr">
@@ -7283,13 +7278,13 @@
       <c r="AE41" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="AF41" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG41" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF41" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG41" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AH41" s="48" t="inlineStr">
         <is>
@@ -7322,7 +7317,7 @@
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
@@ -7332,7 +7327,7 @@
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>57215550013</t>
+          <t>58917134900</t>
         </is>
       </c>
       <c r="D42" s="35" t="inlineStr">
@@ -7420,10 +7415,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U42" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U42" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="V42" s="39" t="inlineStr">
         <is>
@@ -7435,13 +7428,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X42" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X42" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="Y42" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="40" t="inlineStr">
         <is>
@@ -7464,18 +7455,20 @@
         </is>
       </c>
       <c r="AD42" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE42" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF42" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG42" s="28" t="n">
-        <v>1</v>
+      <c r="AG42" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH42" s="43" t="inlineStr">
         <is>
@@ -7492,23 +7485,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK42" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL42" s="59" t="n">
-        <v>1</v>
+      <c r="AK42" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL42" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM42" s="44" t="n">
         <v>2</v>
       </c>
       <c r="AN42" s="45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="46" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Angela Patricia Barreto Maya</t>
         </is>
       </c>
       <c r="B43" s="47" t="inlineStr">
@@ -7518,7 +7515,7 @@
       </c>
       <c r="C43" s="47" t="inlineStr">
         <is>
-          <t>58917134900</t>
+          <t>59269721500</t>
         </is>
       </c>
       <c r="D43" s="48" t="inlineStr">
@@ -7591,10 +7588,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R43" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S43" s="48" t="inlineStr">
         <is>
@@ -7606,24 +7601,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U43" s="53" t="n">
-        <v>1</v>
+      <c r="U43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V43" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W43" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X43" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="Y43" s="49" t="n">
-        <v>2</v>
+      <c r="Y43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z43" s="48" t="inlineStr">
         <is>
@@ -7645,11 +7642,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD43" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE43" s="51" t="n">
-        <v>2</v>
+      <c r="AD43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF43" s="48" t="inlineStr">
         <is>
@@ -7687,16 +7688,16 @@
         </is>
       </c>
       <c r="AM43" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN43" s="45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="33" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra</t>
+          <t>Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
@@ -7706,7 +7707,7 @@
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>58803522300</t>
+          <t>57197327858</t>
         </is>
       </c>
       <c r="D44" s="35" t="inlineStr">
@@ -7724,10 +7725,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="H44" s="35" t="inlineStr">
         <is>
@@ -7739,10 +7738,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J44" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J44" s="37" t="n">
+        <v>2</v>
       </c>
       <c r="K44" s="38" t="inlineStr">
         <is>
@@ -7774,21 +7771,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q44" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" s="17" t="n">
-        <v>1</v>
+      <c r="Q44" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R44" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S44" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T44" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T44" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="U44" s="39" t="inlineStr">
         <is>
@@ -7800,21 +7799,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W44" s="56" t="n">
-        <v>1</v>
+      <c r="W44" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X44" s="57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y44" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z44" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z44" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="24" t="n">
         <v>1</v>
@@ -7829,13 +7828,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD44" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD44" s="41" t="n">
+        <v>1</v>
       </c>
       <c r="AE44" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF44" s="43" t="inlineStr">
         <is>
@@ -7867,8 +7864,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL44" s="59" t="n">
-        <v>1</v>
+      <c r="AL44" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM44" s="44" t="n">
         <v>1</v>
@@ -7880,7 +7879,7 @@
     <row r="45">
       <c r="A45" s="46" t="inlineStr">
         <is>
-          <t>Angela Patricia Barreto Maya</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="B45" s="47" t="inlineStr">
@@ -7890,7 +7889,7 @@
       </c>
       <c r="C45" s="47" t="inlineStr">
         <is>
-          <t>59269721500</t>
+          <t>7005142049</t>
         </is>
       </c>
       <c r="D45" s="48" t="inlineStr">
@@ -7908,10 +7907,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G45" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H45" s="48" t="inlineStr">
         <is>
@@ -7923,10 +7920,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J45" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="K45" s="48" t="inlineStr">
         <is>
@@ -7943,10 +7938,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N45" s="53" t="n">
+        <v>4</v>
       </c>
       <c r="O45" s="48" t="inlineStr">
         <is>
@@ -7958,13 +7951,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R45" s="49" t="n">
-        <v>1</v>
+      <c r="Q45" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="R45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S45" s="48" t="inlineStr">
         <is>
@@ -7986,16 +7979,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W45" s="50" t="n">
-        <v>1</v>
+      <c r="W45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X45" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="Y45" s="49" t="n">
+        <v>2</v>
       </c>
       <c r="Z45" s="48" t="inlineStr">
         <is>
@@ -8007,25 +8000,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB45" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="AC45" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD45" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE45" s="51" t="n">
+        <v>9</v>
       </c>
       <c r="AF45" s="48" t="inlineStr">
         <is>
@@ -8042,10 +8029,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI45" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AJ45" s="48" t="inlineStr">
         <is>
@@ -8057,22 +8042,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL45" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM45" s="44" t="n">
         <v>1</v>
       </c>
       <c r="AN45" s="45" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="33" t="inlineStr">
         <is>
-          <t>Oscar Acevedo Patiño</t>
+          <t>Mauro Antonio Gonzalez Sierra</t>
         </is>
       </c>
       <c r="B46" s="34" t="inlineStr">
@@ -8082,7 +8065,7 @@
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>57197327858</t>
+          <t>58803522300</t>
         </is>
       </c>
       <c r="D46" s="35" t="inlineStr">
@@ -8100,8 +8083,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="10" t="n">
-        <v>1</v>
+      <c r="G46" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H46" s="35" t="inlineStr">
         <is>
@@ -8113,8 +8098,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J46" s="37" t="n">
-        <v>2</v>
+      <c r="J46" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K46" s="38" t="inlineStr">
         <is>
@@ -8146,23 +8133,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q46" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R46" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q46" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="S46" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T46" s="19" t="n">
-        <v>2</v>
+      <c r="T46" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U46" s="39" t="inlineStr">
         <is>
@@ -8174,21 +8159,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W46" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W46" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="X46" s="57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y46" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z46" s="23" t="n">
-        <v>1</v>
+      <c r="Z46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA46" s="24" t="n">
         <v>1</v>
@@ -8203,11 +8188,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD46" s="41" t="n">
-        <v>1</v>
+      <c r="AD46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE46" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF46" s="43" t="inlineStr">
         <is>
@@ -8239,10 +8226,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL46" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL46" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM46" s="44" t="n">
         <v>1</v>
@@ -8254,7 +8239,7 @@
     <row r="47">
       <c r="A47" s="46" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="B47" s="47" t="inlineStr">
@@ -8264,7 +8249,7 @@
       </c>
       <c r="C47" s="47" t="inlineStr">
         <is>
-          <t>7005142049</t>
+          <t>57205400052</t>
         </is>
       </c>
       <c r="D47" s="48" t="inlineStr">
@@ -8282,8 +8267,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="53" t="n">
-        <v>1</v>
+      <c r="G47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H47" s="48" t="inlineStr">
         <is>
@@ -8295,136 +8282,144 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J47" s="51" t="n">
+      <c r="J47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q47" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="K47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N47" s="53" t="n">
+      <c r="R47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X47" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z47" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD47" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL47" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="O47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q47" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="R47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X47" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB47" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD47" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE47" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI47" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL47" s="51" t="n">
-        <v>1</v>
-      </c>
       <c r="AM47" s="44" t="n">
         <v>1</v>
       </c>
       <c r="AN47" s="45" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -11539,7 +11534,7 @@
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Elias Rafael Geney Castro</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
@@ -11549,7 +11544,7 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>57204842254</t>
+          <t>57427876200</t>
         </is>
       </c>
       <c r="D66" s="35" t="inlineStr">
@@ -11557,8 +11552,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E66" s="8" t="n">
-        <v>1</v>
+      <c r="E66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
@@ -11575,11 +11572,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I66" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="37" t="n">
-        <v>1</v>
+      <c r="I66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K66" s="38" t="inlineStr">
         <is>
@@ -11596,25 +11597,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N66" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N66" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O66" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P66" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q66" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P66" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R66" s="39" t="inlineStr">
         <is>
@@ -11656,13 +11651,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z66" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA66" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="AB66" s="40" t="inlineStr">
         <is>
@@ -11680,8 +11675,10 @@
       <c r="AE66" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="AF66" s="27" t="n">
-        <v>1</v>
+      <c r="AF66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG66" s="28" t="n">
         <v>1</v>
@@ -11691,10 +11688,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI66" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="AJ66" s="43" t="inlineStr">
         <is>
@@ -11717,7 +11712,7 @@
     <row r="67">
       <c r="A67" s="46" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="B67" s="47" t="inlineStr">
@@ -11727,7 +11722,7 @@
       </c>
       <c r="C67" s="47" t="inlineStr">
         <is>
-          <t>57427876200</t>
+          <t>57201036449</t>
         </is>
       </c>
       <c r="D67" s="48" t="inlineStr">
@@ -11780,34 +11775,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N67" s="53" t="n">
-        <v>1</v>
+      <c r="N67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O67" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P67" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="51" t="n">
-        <v>1</v>
+      <c r="P67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R67" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S67" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="U67" s="48" t="inlineStr">
         <is>
@@ -11819,15 +11816,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W67" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="X67" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="Y67" s="48" t="inlineStr">
         <is>
@@ -11839,8 +11832,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA67" s="58" t="n">
-        <v>1</v>
+      <c r="AA67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AB67" s="48" t="inlineStr">
         <is>
@@ -11852,27 +11847,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD67" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE67" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG67" s="52" t="n">
-        <v>1</v>
+      <c r="AD67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF67" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH67" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AI67" s="53" t="n">
-        <v>1</v>
+      <c r="AI67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AJ67" s="48" t="inlineStr">
         <is>
@@ -11880,13 +11881,13 @@
         </is>
       </c>
       <c r="AK67" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL67" s="51" t="n">
         <v>2</v>
       </c>
       <c r="AM67" s="44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN67" s="45" t="n">
         <v>4</v>
@@ -11895,7 +11896,7 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
@@ -11905,7 +11906,7 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>57201036449</t>
+          <t>57204842254</t>
         </is>
       </c>
       <c r="D68" s="35" t="inlineStr">
@@ -11913,10 +11914,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E68" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
@@ -11933,15 +11932,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I68" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="K68" s="38" t="inlineStr">
         <is>
@@ -11983,11 +11978,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S68" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T68" s="19" t="n">
-        <v>1</v>
+      <c r="S68" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T68" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U68" s="39" t="inlineStr">
         <is>
@@ -11999,21 +11998,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W68" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="X68" s="57" t="n">
-        <v>2</v>
+      <c r="W68" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X68" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y68" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z68" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="40" t="inlineStr">
         <is>
@@ -12030,18 +12031,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD68" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="42" t="n">
+        <v>1</v>
       </c>
       <c r="AF68" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG68" s="43" t="inlineStr">
         <is>
@@ -12067,13 +12064,13 @@
         <v>1</v>
       </c>
       <c r="AL68" s="59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM68" s="44" t="n">
         <v>3</v>
       </c>
       <c r="AN68" s="45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -12764,7 +12761,7 @@
         <v>1</v>
       </c>
       <c r="AE72" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF72" s="43" t="inlineStr">
         <is>
@@ -12799,7 +12796,7 @@
         <v>2</v>
       </c>
       <c r="AN72" s="45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -14777,32 +14774,32 @@
         <v>1</v>
       </c>
       <c r="AG84" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH84" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI84" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ84" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK84" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="AH84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI84" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ84" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK84" s="45" t="n">
+      <c r="AL84" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="AL84" s="59" t="n">
-        <v>6</v>
-      </c>
       <c r="AM84" s="44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN84" s="45" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85">
@@ -15287,10 +15284,8 @@
       <c r="AG87" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="AH87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH87" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AI87" s="48" t="inlineStr">
         <is>
@@ -15303,16 +15298,16 @@
         </is>
       </c>
       <c r="AK87" s="50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL87" s="51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AM87" s="44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN87" s="45" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88">
@@ -16357,7 +16352,7 @@
         </is>
       </c>
       <c r="AE93" s="51" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF93" s="48" t="inlineStr">
         <is>
@@ -16388,13 +16383,13 @@
         </is>
       </c>
       <c r="AL93" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM93" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AN93" s="45" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
@@ -21163,7 +21158,7 @@
         <v>3</v>
       </c>
       <c r="AF27" s="49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG27" s="48" t="inlineStr">
         <is>
@@ -21187,13 +21182,13 @@
         <v>3</v>
       </c>
       <c r="AL27" s="51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM27" s="44" t="n">
         <v>9</v>
       </c>
       <c r="AN27" s="45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -21654,10 +21649,8 @@
       <c r="AE30" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="AF30" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF30" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG30" s="28" t="n">
         <v>1</v>
@@ -21678,22 +21671,22 @@
         </is>
       </c>
       <c r="AK30" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL30" s="59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM30" s="44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN30" s="45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="46" t="inlineStr">
         <is>
-          <t>Deyler Rafael Castilla Caballero</t>
+          <t>Mary Judith Arias Tapia</t>
         </is>
       </c>
       <c r="B31" s="47" t="inlineStr">
@@ -21703,16 +21696,14 @@
       </c>
       <c r="C31" s="47" t="inlineStr">
         <is>
-          <t>57024211000</t>
+          <t>57219403758</t>
         </is>
       </c>
       <c r="D31" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E31" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="F31" s="48" t="inlineStr">
         <is>
@@ -21729,16 +21720,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I31" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="J31" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="49" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L31" s="48" t="inlineStr">
         <is>
@@ -21750,24 +21741,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N31" s="53" t="n">
-        <v>1</v>
+      <c r="N31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O31" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P31" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="R31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R31" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S31" s="48" t="inlineStr">
         <is>
@@ -21789,23 +21784,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z31" s="52" t="n">
-        <v>2</v>
+      <c r="W31" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA31" s="48" t="inlineStr">
         <is>
@@ -21823,13 +21814,13 @@
         </is>
       </c>
       <c r="AD31" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE31" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF31" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG31" s="48" t="inlineStr">
         <is>
@@ -21851,25 +21842,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK31" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK31" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="AL31" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM31" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN31" s="45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>Rafael David Mendez Anillo</t>
+          <t>Deyler Rafael Castilla Caballero</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
@@ -21879,7 +21868,7 @@
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>57903699900</t>
+          <t>57024211000</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
@@ -21905,16 +21894,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="36" t="n">
-        <v>1</v>
+      <c r="I32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J32" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K32" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="L32" s="38" t="inlineStr">
         <is>
@@ -21926,25 +21915,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N32" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N32" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O32" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P32" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q32" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P32" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="R32" s="39" t="inlineStr">
         <is>
@@ -21981,13 +21964,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y32" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Y32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z32" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="AA32" s="40" t="inlineStr">
         <is>
@@ -22005,16 +21988,18 @@
         </is>
       </c>
       <c r="AD32" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE32" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF32" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="AG32" s="28" t="n">
-        <v>1</v>
+      <c r="AG32" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH32" s="43" t="inlineStr">
         <is>
@@ -22031,23 +22016,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK32" s="45" t="n">
-        <v>2</v>
+      <c r="AK32" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AL32" s="59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM32" s="44" t="n">
         <v>4</v>
       </c>
       <c r="AN32" s="45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Rafael David Mendez Anillo</t>
         </is>
       </c>
       <c r="B33" s="47" t="inlineStr">
@@ -22057,19 +22044,21 @@
       </c>
       <c r="C33" s="47" t="inlineStr">
         <is>
-          <t>57210822856</t>
+          <t>57903699900</t>
         </is>
       </c>
       <c r="D33" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="58" t="n">
-        <v>1</v>
+      <c r="F33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G33" s="48" t="inlineStr">
         <is>
@@ -22082,13 +22071,15 @@
         </is>
       </c>
       <c r="I33" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" s="49" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L33" s="48" t="inlineStr">
         <is>
@@ -22100,19 +22091,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N33" s="53" t="n">
-        <v>4</v>
+      <c r="N33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P33" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="51" t="n">
-        <v>7</v>
+      <c r="P33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R33" s="48" t="inlineStr">
         <is>
@@ -22129,8 +22126,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U33" s="53" t="n">
-        <v>7</v>
+      <c r="U33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V33" s="48" t="inlineStr">
         <is>
@@ -22142,24 +22141,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X33" s="51" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y33" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="Z33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AA33" s="58" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB33" s="53" t="n">
-        <v>6</v>
+      <c r="AA33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC33" s="48" t="inlineStr">
         <is>
@@ -22170,20 +22173,18 @@
         <v>1</v>
       </c>
       <c r="AE33" s="51" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH33" s="58" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AF33" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI33" s="48" t="inlineStr">
         <is>
@@ -22195,25 +22196,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK33" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="AL33" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM33" s="44" t="n">
         <v>4</v>
       </c>
       <c r="AN33" s="45" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="33" t="inlineStr">
         <is>
-          <t>Mary Judith Arias Tapia</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="B34" s="34" t="inlineStr">
@@ -22223,19 +22222,19 @@
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>57219403758</t>
+          <t>57210822856</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E34" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G34" s="35" t="inlineStr">
         <is>
@@ -22251,89 +22250,81 @@
         <v>2</v>
       </c>
       <c r="J34" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="R34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="V34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W34" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X34" s="57" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA34" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="K34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q34" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R34" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T34" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U34" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V34" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W34" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA34" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB34" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB34" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="AC34" s="40" t="inlineStr">
         <is>
@@ -22344,20 +22335,20 @@
         <v>1</v>
       </c>
       <c r="AE34" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="27" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="AF34" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG34" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AH34" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH34" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="AI34" s="43" t="inlineStr">
         <is>
@@ -22381,7 +22372,7 @@
         <v>4</v>
       </c>
       <c r="AN34" s="45" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -23109,7 +23100,7 @@
     <row r="39">
       <c r="A39" s="46" t="inlineStr">
         <is>
-          <t>Jenifer Yoris Vasquez Aguilar</t>
+          <t>Luis Ángel Porto Hernández</t>
         </is>
       </c>
       <c r="B39" s="47" t="inlineStr">
@@ -23119,7 +23110,7 @@
       </c>
       <c r="C39" s="47" t="inlineStr">
         <is>
-          <t>57205400052</t>
+          <t>57804909800</t>
         </is>
       </c>
       <c r="D39" s="48" t="inlineStr">
@@ -23172,8 +23163,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N39" s="53" t="n">
-        <v>1</v>
+      <c r="N39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O39" s="48" t="inlineStr">
         <is>
@@ -23185,8 +23178,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q39" s="51" t="n">
-        <v>4</v>
+      <c r="Q39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R39" s="48" t="inlineStr">
         <is>
@@ -23203,8 +23198,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U39" s="53" t="n">
-        <v>2</v>
+      <c r="U39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V39" s="48" t="inlineStr">
         <is>
@@ -23216,78 +23213,80 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X39" s="51" t="n">
-        <v>2</v>
+      <c r="X39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y39" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z39" s="52" t="n">
-        <v>1</v>
+      <c r="Z39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA39" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AB39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB39" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC39" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD39" s="50" t="n">
-        <v>1</v>
+      <c r="AD39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE39" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH39" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ39" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK39" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL39" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN39" s="45" t="n">
         <v>3</v>
-      </c>
-      <c r="AF39" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ39" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK39" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL39" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM39" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN39" s="45" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>Luis Ángel Porto Hernández</t>
+          <t>Efraín Andrés Rodríguez Gasca</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
@@ -23297,7 +23296,7 @@
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>57804909800</t>
+          <t>57197028938</t>
         </is>
       </c>
       <c r="D40" s="35" t="inlineStr">
@@ -23405,10 +23404,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y40" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Y40" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="Z40" s="40" t="inlineStr">
         <is>
@@ -23420,18 +23417,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB40" s="25" t="n">
-        <v>1</v>
+      <c r="AB40" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC40" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD40" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD40" s="41" t="n">
+        <v>1</v>
       </c>
       <c r="AE40" s="42" t="n">
         <v>1</v>
@@ -23444,8 +23441,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH40" s="29" t="n">
-        <v>1</v>
+      <c r="AH40" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI40" s="43" t="inlineStr">
         <is>
@@ -23458,22 +23457,22 @@
         </is>
       </c>
       <c r="AK40" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL40" s="59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM40" s="44" t="n">
         <v>2</v>
       </c>
       <c r="AN40" s="45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="46" t="inlineStr">
         <is>
-          <t>Efraín Andrés Rodríguez Gasca</t>
+          <t>Luz Marina Gómez Hernández</t>
         </is>
       </c>
       <c r="B41" s="47" t="inlineStr">
@@ -23483,7 +23482,7 @@
       </c>
       <c r="C41" s="47" t="inlineStr">
         <is>
-          <t>57197028938</t>
+          <t>57215550013</t>
         </is>
       </c>
       <c r="D41" s="48" t="inlineStr">
@@ -23659,7 +23658,7 @@
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
         <is>
-          <t>Luz Marina Gómez Hernández</t>
+          <t>Jefferson Andres Piedrahita Gonzalez</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
@@ -23669,7 +23668,7 @@
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>57215550013</t>
+          <t>58917134900</t>
         </is>
       </c>
       <c r="D42" s="35" t="inlineStr">
@@ -23757,10 +23756,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U42" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U42" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="V42" s="39" t="inlineStr">
         <is>
@@ -23772,18 +23769,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X42" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="X42" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="Y42" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z42" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="40" t="inlineStr">
         <is>
@@ -23801,13 +23794,15 @@
         </is>
       </c>
       <c r="AD42" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE42" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AF42" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AG42" s="43" t="inlineStr">
         <is>
@@ -23829,23 +23824,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK42" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL42" s="59" t="n">
-        <v>1</v>
+      <c r="AK42" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL42" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM42" s="44" t="n">
         <v>2</v>
       </c>
       <c r="AN42" s="45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="46" t="inlineStr">
         <is>
-          <t>Jefferson Andres Piedrahita Gonzalez</t>
+          <t>Angela Patricia Barreto Maya</t>
         </is>
       </c>
       <c r="B43" s="47" t="inlineStr">
@@ -23855,7 +23854,7 @@
       </c>
       <c r="C43" s="47" t="inlineStr">
         <is>
-          <t>58917134900</t>
+          <t>59269721500</t>
         </is>
       </c>
       <c r="D43" s="48" t="inlineStr">
@@ -23928,10 +23927,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R43" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S43" s="48" t="inlineStr">
         <is>
@@ -23943,27 +23940,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U43" s="53" t="n">
-        <v>1</v>
+      <c r="U43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V43" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W43" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W43" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="X43" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="Y43" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="52" t="n">
-        <v>1</v>
+      <c r="Y43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA43" s="48" t="inlineStr">
         <is>
@@ -23980,11 +23981,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD43" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE43" s="51" t="n">
-        <v>2</v>
+      <c r="AD43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE43" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF43" s="48" t="inlineStr">
         <is>
@@ -24022,16 +24027,16 @@
         </is>
       </c>
       <c r="AM43" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN43" s="45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="33" t="inlineStr">
         <is>
-          <t>Mauro Antonio Gonzalez Sierra</t>
+          <t>Oscar Acevedo Patiño</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
@@ -24041,7 +24046,7 @@
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>58803522300</t>
+          <t>57197327858</t>
         </is>
       </c>
       <c r="D44" s="35" t="inlineStr">
@@ -24054,10 +24059,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F44" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G44" s="35" t="inlineStr">
         <is>
@@ -24074,10 +24077,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J44" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J44" s="37" t="n">
+        <v>2</v>
       </c>
       <c r="K44" s="38" t="inlineStr">
         <is>
@@ -24109,21 +24110,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q44" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" s="17" t="n">
-        <v>1</v>
+      <c r="Q44" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R44" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S44" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T44" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T44" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="U44" s="39" t="inlineStr">
         <is>
@@ -24135,21 +24138,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W44" s="56" t="n">
-        <v>1</v>
+      <c r="W44" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X44" s="57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y44" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z44" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z44" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="24" t="n">
         <v>1</v>
@@ -24164,13 +24167,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD44" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD44" s="41" t="n">
+        <v>1</v>
       </c>
       <c r="AE44" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF44" s="43" t="inlineStr">
         <is>
@@ -24202,8 +24203,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL44" s="59" t="n">
-        <v>1</v>
+      <c r="AL44" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM44" s="44" t="n">
         <v>1</v>
@@ -24215,7 +24218,7 @@
     <row r="45">
       <c r="A45" s="46" t="inlineStr">
         <is>
-          <t>Angela Patricia Barreto Maya</t>
+          <t>Jose Luis Villa Ramirez</t>
         </is>
       </c>
       <c r="B45" s="47" t="inlineStr">
@@ -24225,7 +24228,7 @@
       </c>
       <c r="C45" s="47" t="inlineStr">
         <is>
-          <t>59269721500</t>
+          <t>7005142049</t>
         </is>
       </c>
       <c r="D45" s="48" t="inlineStr">
@@ -24238,15 +24241,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F45" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H45" s="48" t="inlineStr">
         <is>
@@ -24258,10 +24257,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J45" s="51" t="n">
+        <v>4</v>
       </c>
       <c r="K45" s="48" t="inlineStr">
         <is>
@@ -24273,15 +24270,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M45" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="N45" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="O45" s="48" t="inlineStr">
         <is>
@@ -24293,13 +24286,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R45" s="49" t="n">
-        <v>1</v>
+      <c r="Q45" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="R45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S45" s="48" t="inlineStr">
         <is>
@@ -24311,56 +24304,46 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U45" s="53" t="n">
+        <v>3</v>
       </c>
       <c r="V45" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W45" s="50" t="n">
-        <v>1</v>
+      <c r="W45" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X45" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="Y45" s="49" t="n">
+        <v>2</v>
       </c>
       <c r="Z45" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AA45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA45" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB45" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="AC45" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD45" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE45" s="51" t="n">
+        <v>9</v>
       </c>
       <c r="AF45" s="48" t="inlineStr">
         <is>
@@ -24372,10 +24355,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH45" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="AI45" s="48" t="inlineStr">
         <is>
@@ -24392,22 +24373,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL45" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL45" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AM45" s="44" t="n">
         <v>1</v>
       </c>
       <c r="AN45" s="45" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="33" t="inlineStr">
         <is>
-          <t>Oscar Acevedo Patiño</t>
+          <t>Mauro Antonio Gonzalez Sierra</t>
         </is>
       </c>
       <c r="B46" s="34" t="inlineStr">
@@ -24417,7 +24396,7 @@
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>57197327858</t>
+          <t>58803522300</t>
         </is>
       </c>
       <c r="D46" s="35" t="inlineStr">
@@ -24430,8 +24409,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>1</v>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
         <is>
@@ -24448,8 +24429,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J46" s="37" t="n">
-        <v>2</v>
+      <c r="J46" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K46" s="38" t="inlineStr">
         <is>
@@ -24481,23 +24464,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q46" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R46" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q46" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="S46" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T46" s="19" t="n">
-        <v>2</v>
+      <c r="T46" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U46" s="39" t="inlineStr">
         <is>
@@ -24509,21 +24490,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W46" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W46" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="X46" s="57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y46" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z46" s="23" t="n">
-        <v>1</v>
+      <c r="Z46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA46" s="24" t="n">
         <v>1</v>
@@ -24538,11 +24519,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD46" s="41" t="n">
-        <v>1</v>
+      <c r="AD46" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE46" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF46" s="43" t="inlineStr">
         <is>
@@ -24574,10 +24557,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL46" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL46" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AM46" s="44" t="n">
         <v>1</v>
@@ -24589,7 +24570,7 @@
     <row r="47">
       <c r="A47" s="46" t="inlineStr">
         <is>
-          <t>Jose Luis Villa Ramirez</t>
+          <t>Jenifer Yoris Vasquez Aguilar</t>
         </is>
       </c>
       <c r="B47" s="47" t="inlineStr">
@@ -24599,7 +24580,7 @@
       </c>
       <c r="C47" s="47" t="inlineStr">
         <is>
-          <t>7005142049</t>
+          <t>57205400052</t>
         </is>
       </c>
       <c r="D47" s="48" t="inlineStr">
@@ -24612,11 +24593,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F47" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="53" t="n">
-        <v>1</v>
+      <c r="F47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H47" s="48" t="inlineStr">
         <is>
@@ -24628,112 +24613,120 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J47" s="51" t="n">
+      <c r="J47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q47" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="K47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="58" t="n">
+      <c r="R47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U47" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X47" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z47" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD47" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH47" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI47" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="N47" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="O47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q47" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="R47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U47" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="V47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X47" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA47" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB47" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD47" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE47" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH47" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI47" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="AJ47" s="48" t="inlineStr">
         <is>
           <t>—</t>
@@ -24745,13 +24738,13 @@
         </is>
       </c>
       <c r="AL47" s="51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM47" s="44" t="n">
         <v>1</v>
       </c>
       <c r="AN47" s="45" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -27860,7 +27853,7 @@
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>Elias Rafael Geney Castro</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
@@ -27870,11 +27863,13 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>57204842254</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>1</v>
+          <t>57427876200</t>
+        </is>
+      </c>
+      <c r="D66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E66" s="35" t="inlineStr">
         <is>
@@ -27896,11 +27891,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I66" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="37" t="n">
-        <v>1</v>
+      <c r="I66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K66" s="38" t="inlineStr">
         <is>
@@ -27917,25 +27916,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N66" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N66" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O66" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P66" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q66" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P66" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R66" s="39" t="inlineStr">
         <is>
@@ -27977,13 +27970,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z66" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA66" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="AB66" s="40" t="inlineStr">
         <is>
@@ -28001,23 +27994,21 @@
       <c r="AE66" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="AF66" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AF66" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG66" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="AH66" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AI66" s="43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI66" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="AJ66" s="43" t="inlineStr">
         <is>
@@ -28040,7 +28031,7 @@
     <row r="67">
       <c r="A67" s="46" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="B67" s="47" t="inlineStr">
@@ -28050,7 +28041,7 @@
       </c>
       <c r="C67" s="47" t="inlineStr">
         <is>
-          <t>57427876200</t>
+          <t>57201036449</t>
         </is>
       </c>
       <c r="D67" s="48" t="inlineStr">
@@ -28103,34 +28094,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N67" s="53" t="n">
-        <v>1</v>
+      <c r="N67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O67" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P67" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="51" t="n">
-        <v>1</v>
+      <c r="P67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R67" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S67" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" s="58" t="n">
+        <v>1</v>
       </c>
       <c r="U67" s="48" t="inlineStr">
         <is>
@@ -28142,15 +28135,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W67" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="X67" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="Y67" s="48" t="inlineStr">
         <is>
@@ -28162,8 +28151,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA67" s="58" t="n">
-        <v>1</v>
+      <c r="AA67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AB67" s="48" t="inlineStr">
         <is>
@@ -28175,27 +28166,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD67" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE67" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF67" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG67" s="52" t="n">
-        <v>1</v>
+      <c r="AD67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF67" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH67" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AI67" s="53" t="n">
-        <v>1</v>
+      <c r="AI67" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AJ67" s="48" t="inlineStr">
         <is>
@@ -28203,13 +28200,13 @@
         </is>
       </c>
       <c r="AK67" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL67" s="51" t="n">
         <v>2</v>
       </c>
       <c r="AM67" s="44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN67" s="45" t="n">
         <v>4</v>
@@ -28218,7 +28215,7 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
@@ -28228,13 +28225,11 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>57201036449</t>
-        </is>
-      </c>
-      <c r="D68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57204842254</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="E68" s="35" t="inlineStr">
         <is>
@@ -28256,15 +28251,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I68" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="K68" s="38" t="inlineStr">
         <is>
@@ -28306,11 +28297,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S68" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T68" s="19" t="n">
-        <v>1</v>
+      <c r="S68" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T68" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U68" s="39" t="inlineStr">
         <is>
@@ -28322,21 +28317,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W68" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="X68" s="57" t="n">
-        <v>2</v>
+      <c r="W68" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X68" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y68" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Z68" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="40" t="inlineStr">
         <is>
@@ -28353,18 +28350,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD68" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="42" t="n">
+        <v>1</v>
       </c>
       <c r="AF68" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG68" s="43" t="inlineStr">
         <is>
@@ -28390,13 +28383,13 @@
         <v>1</v>
       </c>
       <c r="AL68" s="59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM68" s="44" t="n">
         <v>3</v>
       </c>
       <c r="AN68" s="45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -29067,10 +29060,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB72" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB72" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="AC72" s="40" t="inlineStr">
         <is>
@@ -29081,7 +29072,7 @@
         <v>1</v>
       </c>
       <c r="AE72" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF72" s="27" t="n">
         <v>1</v>
@@ -29116,7 +29107,7 @@
         <v>2</v>
       </c>
       <c r="AN72" s="45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -31063,7 +31054,7 @@
         <v>31</v>
       </c>
       <c r="AF84" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG84" s="28" t="n">
         <v>3</v>
@@ -31082,16 +31073,16 @@
         </is>
       </c>
       <c r="AK84" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL84" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="AL84" s="59" t="n">
-        <v>6</v>
-      </c>
       <c r="AM84" s="44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN84" s="45" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85">
@@ -31557,10 +31548,8 @@
       <c r="AF87" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="AG87" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG87" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AH87" s="58" t="n">
         <v>1</v>
@@ -31576,16 +31565,16 @@
         </is>
       </c>
       <c r="AK87" s="50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL87" s="51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AM87" s="44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN87" s="45" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88">
@@ -32609,7 +32598,7 @@
         <v>1</v>
       </c>
       <c r="AB93" s="53" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AC93" s="48" t="inlineStr">
         <is>
@@ -32622,7 +32611,7 @@
         </is>
       </c>
       <c r="AE93" s="51" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF93" s="48" t="inlineStr">
         <is>
@@ -32637,10 +32626,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI93" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI93" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AJ93" s="48" t="inlineStr">
         <is>
@@ -32653,13 +32640,13 @@
         </is>
       </c>
       <c r="AL93" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM93" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AN93" s="45" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Centro de Idiomas</t>
+          <t xml:space="preserve"> Centro de Idiomas</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Ciencias Básicas</t>
+          <t xml:space="preserve"> Ciencias Básicas</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Dirección de Humanidades</t>
+          <t xml:space="preserve"> Dirección de Humanidades</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
     <row r="23">
       <c r="A23" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t xml:space="preserve"> Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
@@ -13763,7 +13763,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Escuela de Negocios, Leyes y Sociedad</t>
+          <t xml:space="preserve"> Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
     <row r="83">
       <c r="A83" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Escuela de Transformación Digital</t>
+          <t xml:space="preserve"> Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Centro de Idiomas</t>
+          <t xml:space="preserve"> Centro de Idiomas</t>
         </is>
       </c>
     </row>
@@ -24589,7 +24589,7 @@
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Ciencias Básicas</t>
+          <t xml:space="preserve"> Ciencias Básicas</t>
         </is>
       </c>
     </row>
@@ -27958,7 +27958,7 @@
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Dirección de Humanidades</t>
+          <t xml:space="preserve"> Dirección de Humanidades</t>
         </is>
       </c>
     </row>
@@ -28223,7 +28223,7 @@
     <row r="23">
       <c r="A23" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Escuela de Ingeniería, Arquitectura y Diseño</t>
+          <t xml:space="preserve"> Escuela de Ingeniería, Arquitectura y Diseño</t>
         </is>
       </c>
     </row>
@@ -36534,7 +36534,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Escuela de Negocios, Leyes y Sociedad</t>
+          <t xml:space="preserve"> Escuela de Negocios, Leyes y Sociedad</t>
         </is>
       </c>
     </row>
@@ -42483,7 +42483,7 @@
     <row r="83">
       <c r="A83" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🏫  Escuela de Transformación Digital</t>
+          <t xml:space="preserve"> Escuela de Transformación Digital</t>
         </is>
       </c>
     </row>

--- a/autores_pivot_cuartiles.xlsx
+++ b/autores_pivot_cuartiles.xlsx
@@ -3093,7 +3093,7 @@
     <row r="13">
       <c r="A13" s="46" t="inlineStr">
         <is>
-          <t>Edisson Chavarro Mesa</t>
+          <t>Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="B13" s="47" t="inlineStr">
@@ -3103,11 +3103,13 @@
       </c>
       <c r="C13" s="47" t="inlineStr">
         <is>
-          <t>57188841051</t>
-        </is>
-      </c>
-      <c r="D13" s="49" t="n">
-        <v>1</v>
+          <t>57190688459</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E13" s="48" t="inlineStr">
         <is>
@@ -3129,11 +3131,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="50" t="n">
-        <v>1</v>
+      <c r="I13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J13" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="48" t="inlineStr">
         <is>
@@ -3145,8 +3149,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M13" s="59" t="n">
-        <v>1</v>
+      <c r="M13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N13" s="53" t="n">
         <v>1</v>
@@ -3157,10 +3163,10 @@
         </is>
       </c>
       <c r="P13" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R13" s="48" t="inlineStr">
         <is>
@@ -3192,8 +3198,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X13" s="51" t="n">
-        <v>1</v>
+      <c r="X13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y13" s="48" t="inlineStr">
         <is>
@@ -3210,10 +3218,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB13" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC13" s="48" t="inlineStr">
         <is>
@@ -3259,17 +3265,15 @@
         </is>
       </c>
       <c r="AL13" s="51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM13" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AN13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AN13" s="52" t="n">
+        <v>2</v>
       </c>
       <c r="AO13" s="48" t="inlineStr">
         <is>
@@ -3286,13 +3290,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AR13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AR13" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="AS13" s="51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AT13" s="48" t="inlineStr">
         <is>
@@ -3324,20 +3326,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AZ13" s="51" t="n">
-        <v>3</v>
+      <c r="AZ13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="BA13" s="44" t="n">
         <v>3</v>
       </c>
       <c r="BB13" s="45" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>Alberto Patiño Vanegas</t>
+          <t>Jorge Luis Villalba Acevedo</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
@@ -3347,7 +3351,7 @@
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>57190688459</t>
+          <t>57918628600</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
@@ -3380,8 +3384,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="43" t="n">
-        <v>3</v>
+      <c r="J14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K14" s="36" t="inlineStr">
         <is>
@@ -3398,59 +3404,55 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N14" s="15" t="n">
-        <v>1</v>
+      <c r="N14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O14" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P14" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="55" t="n">
-        <v>1</v>
+      <c r="P14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R14" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S14" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="T14" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U14" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="V14" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y14" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W14" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="Z14" s="40" t="inlineStr">
         <is>
@@ -3462,21 +3464,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB14" s="25" t="n">
-        <v>1</v>
+      <c r="AB14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC14" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD14" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD14" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="AE14" s="57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AF14" s="41" t="inlineStr">
         <is>
@@ -3493,20 +3495,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI14" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI14" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="AJ14" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK14" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK14" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="AL14" s="58" t="n">
         <v>3</v>
@@ -3516,76 +3514,78 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="n">
+      <c r="AN14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AP14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AQ14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS14" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AV14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AX14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AY14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ14" s="55" t="n">
         <v>2</v>
-      </c>
-      <c r="AO14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AQ14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR14" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS14" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AW14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AX14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AY14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
       </c>
       <c r="BA14" s="44" t="n">
         <v>3</v>
       </c>
       <c r="BB14" s="45" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis Villalba Acevedo</t>
+          <t>Edisson Chavarro Mesa</t>
         </is>
       </c>
       <c r="B15" s="47" t="inlineStr">
@@ -3595,13 +3595,11 @@
       </c>
       <c r="C15" s="47" t="inlineStr">
         <is>
-          <t>57918628600</t>
-        </is>
-      </c>
-      <c r="D15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57188841051</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="E15" s="48" t="inlineStr">
         <is>
@@ -3623,15 +3621,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I15" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="K15" s="48" t="inlineStr">
         <is>
@@ -3643,60 +3637,60 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M15" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="O15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P15" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="51" t="n">
+        <v>3</v>
       </c>
       <c r="R15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S15" s="52" t="n">
-        <v>1</v>
+      <c r="S15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="T15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U15" s="53" t="n">
-        <v>1</v>
+      <c r="U15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W15" s="50" t="n">
-        <v>1</v>
+      <c r="W15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X15" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y15" s="49" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Y15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z15" s="48" t="inlineStr">
         <is>
@@ -3718,11 +3712,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD15" s="50" t="n">
-        <v>1</v>
+      <c r="AD15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE15" s="51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF15" s="48" t="inlineStr">
         <is>
@@ -3755,7 +3751,7 @@
         </is>
       </c>
       <c r="AL15" s="51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM15" s="48" t="inlineStr">
         <is>
@@ -3788,46 +3784,46 @@
         </is>
       </c>
       <c r="AS15" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AV15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AX15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AY15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ15" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="AT15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AW15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AX15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AY15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ15" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="BA15" s="44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB15" s="45" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -4080,16 +4076,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AZ16" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AZ16" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="BA16" s="44" t="n">
         <v>2</v>
       </c>
       <c r="BB16" s="45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -7209,7 +7203,7 @@
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Mary Judith Arias Tapia</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
@@ -7219,11 +7213,13 @@
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>57210822856</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>1</v>
+          <t>57219403758</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E32" s="35" t="inlineStr">
         <is>
@@ -7245,24 +7241,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="L32" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M32" s="14" t="n">
-        <v>2</v>
+      <c r="M32" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N32" s="36" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="Q32" s="55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R32" s="17" t="n">
         <v>2</v>
@@ -7288,13 +7288,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T32" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U32" s="20" t="n">
-        <v>1</v>
+      <c r="T32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V32" s="37" t="inlineStr">
         <is>
@@ -7305,15 +7305,17 @@
         <v>2</v>
       </c>
       <c r="X32" s="39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y32" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z32" s="23" t="n">
-        <v>1</v>
+      <c r="Z32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AA32" s="40" t="inlineStr">
         <is>
@@ -7330,112 +7332,112 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AD32" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE32" s="57" t="n">
-        <v>7</v>
+      <c r="AD32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF32" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG32" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG32" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="AH32" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AI32" s="30" t="n">
+      <c r="AI32" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ32" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK32" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL32" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AP32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AQ32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR32" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="AJ32" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK32" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL32" s="58" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM32" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AN32" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP32" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ32" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR32" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS32" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT32" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU32" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AU32" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="AV32" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AW32" s="15" t="n">
-        <v>1</v>
+      <c r="AW32" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AX32" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AY32" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AY32" s="54" t="n">
+        <v>2</v>
       </c>
       <c r="AZ32" s="55" t="n">
         <v>3</v>
       </c>
       <c r="BA32" s="44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB32" s="45" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>Mary Judith Arias Tapia</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="B33" s="47" t="inlineStr">
@@ -7445,13 +7447,11 @@
       </c>
       <c r="C33" s="47" t="inlineStr">
         <is>
-          <t>57219403758</t>
-        </is>
-      </c>
-      <c r="D33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57210822856</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
@@ -7473,28 +7473,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K33" s="49" t="n">
-        <v>1</v>
+      <c r="I33" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M33" s="59" t="n">
+        <v>2</v>
       </c>
       <c r="N33" s="48" t="inlineStr">
         <is>
@@ -7510,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="Q33" s="51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R33" s="49" t="n">
         <v>2</v>
@@ -7520,13 +7516,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T33" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U33" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V33" s="48" t="inlineStr">
         <is>
@@ -7537,90 +7533,84 @@
         <v>2</v>
       </c>
       <c r="X33" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z33" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD33" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI33" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL33" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AN33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO33" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="Y33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG33" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK33" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM33" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="AQ33" s="48" t="inlineStr">
         <is>
           <t>—</t>
@@ -7630,10 +7620,12 @@
         <v>1</v>
       </c>
       <c r="AS33" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT33" s="49" t="n">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="AT33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AU33" s="48" t="inlineStr">
         <is>
@@ -7645,27 +7637,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AW33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AW33" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AX33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AY33" s="50" t="n">
-        <v>1</v>
+      <c r="AY33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AZ33" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA33" s="44" t="n">
         <v>6</v>
       </c>
       <c r="BB33" s="45" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
@@ -14205,7 +14197,7 @@
         <v>1</v>
       </c>
       <c r="AW60" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX60" s="36" t="inlineStr">
         <is>
@@ -14213,16 +14205,16 @@
         </is>
       </c>
       <c r="AY60" s="54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ60" s="55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA60" s="44" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB60" s="45" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -14411,10 +14403,8 @@
       <c r="AU61" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="AV61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AV61" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AW61" s="48" t="inlineStr">
         <is>
@@ -14427,16 +14417,16 @@
         </is>
       </c>
       <c r="AY61" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ61" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA61" s="44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB61" s="45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
@@ -14912,7 +14902,7 @@
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>Elias Rafael Geney Castro</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
@@ -14922,7 +14912,7 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>57197807415</t>
+          <t>57427876200</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -14975,25 +14965,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N64" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O64" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P64" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R64" s="37" t="inlineStr">
         <is>
@@ -15040,13 +15024,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA64" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB64" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB64" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="AC64" s="40" t="inlineStr">
         <is>
@@ -15089,74 +15073,78 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL64" s="58" t="n">
+      <c r="AL64" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AN64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AQ64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR64" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS64" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT64" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU64" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV64" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW64" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX64" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AY64" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="AM64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AN64" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AQ64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR64" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS64" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT64" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU64" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV64" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AX64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AY64" s="54" t="n">
-        <v>3</v>
-      </c>
       <c r="AZ64" s="55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA64" s="44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB64" s="45" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="B65" s="47" t="inlineStr">
@@ -15166,7 +15154,7 @@
       </c>
       <c r="C65" s="47" t="inlineStr">
         <is>
-          <t>58068307100</t>
+          <t>57197807415</t>
         </is>
       </c>
       <c r="D65" s="48" t="inlineStr">
@@ -15209,8 +15197,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L65" s="52" t="n">
-        <v>1</v>
+      <c r="L65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M65" s="48" t="inlineStr">
         <is>
@@ -15227,11 +15217,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P65" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="51" t="n">
-        <v>1</v>
+      <c r="P65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R65" s="48" t="inlineStr">
         <is>
@@ -15307,70 +15301,66 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH65" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI65" s="53" t="n">
-        <v>1</v>
+      <c r="AH65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AJ65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK65" s="50" t="n">
+      <c r="AK65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL65" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AN65" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="AL65" s="51" t="n">
+      <c r="AO65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AP65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AQ65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR65" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="AM65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AN65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AQ65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AS65" s="51" t="n">
+        <v>5</v>
       </c>
       <c r="AT65" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="AU65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AU65" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV65" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AW65" s="48" t="inlineStr">
         <is>
@@ -15383,22 +15373,22 @@
         </is>
       </c>
       <c r="AY65" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ65" s="51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA65" s="44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB65" s="45" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro</t>
+          <t>Jorge Luis Alvis Arrieta</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
@@ -15408,7 +15398,7 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>57427876200</t>
+          <t>58068307100</t>
         </is>
       </c>
       <c r="D66" s="35" t="inlineStr">
@@ -15451,18 +15441,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L66" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L66" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="M66" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N66" s="15" t="n">
-        <v>1</v>
+      <c r="N66" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O66" s="36" t="inlineStr">
         <is>
@@ -15520,13 +15510,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB66" s="25" t="n">
-        <v>1</v>
+      <c r="AA66" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC66" s="40" t="inlineStr">
         <is>
@@ -15549,30 +15539,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH66" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI66" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH66" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI66" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="AJ66" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK66" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL66" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK66" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL66" s="58" t="n">
+        <v>2</v>
       </c>
       <c r="AM66" s="35" t="inlineStr">
         <is>
@@ -15584,8 +15566,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AO66" s="9" t="n">
-        <v>1</v>
+      <c r="AO66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AP66" s="35" t="inlineStr">
         <is>
@@ -15597,27 +15581,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AR66" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS66" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT66" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU66" s="13" t="n">
-        <v>1</v>
+      <c r="AR66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT66" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU66" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AV66" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AW66" s="15" t="n">
-        <v>1</v>
+      <c r="AW66" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AX66" s="36" t="inlineStr">
         <is>
@@ -15625,10 +15615,10 @@
         </is>
       </c>
       <c r="AY66" s="54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ66" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA66" s="44" t="n">
         <v>5</v>
@@ -15884,7 +15874,7 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
@@ -15894,7 +15884,7 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>57204842254</t>
+          <t>57201036449</t>
         </is>
       </c>
       <c r="D68" s="35" t="inlineStr">
@@ -15927,150 +15917,152 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J68" s="43" t="n">
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF68" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG68" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI68" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ68" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK68" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="K68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S68" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W68" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="X68" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL68" s="58" t="n">
+        <v>2</v>
       </c>
       <c r="AM68" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AN68" s="8" t="n">
-        <v>1</v>
+      <c r="AN68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AO68" s="35" t="inlineStr">
         <is>
@@ -16087,27 +16079,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AR68" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS68" s="43" t="n">
-        <v>1</v>
+      <c r="AR68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AT68" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU68" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AV68" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AW68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AW68" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="AX68" s="36" t="inlineStr">
         <is>
@@ -16118,19 +16114,19 @@
         <v>2</v>
       </c>
       <c r="AZ68" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA68" s="44" t="n">
         <v>4</v>
       </c>
       <c r="BB68" s="45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="46" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="B69" s="47" t="inlineStr">
@@ -16140,7 +16136,7 @@
       </c>
       <c r="C69" s="47" t="inlineStr">
         <is>
-          <t>57201036449</t>
+          <t>57204842254</t>
         </is>
       </c>
       <c r="D69" s="48" t="inlineStr">
@@ -16173,10 +16169,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="K69" s="48" t="inlineStr">
         <is>
@@ -16218,10 +16212,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S69" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="T69" s="48" t="inlineStr">
         <is>
@@ -16238,15 +16230,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W69" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X69" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="Y69" s="48" t="inlineStr">
         <is>
@@ -16288,11 +16276,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AG69" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH69" s="59" t="n">
-        <v>1</v>
+      <c r="AG69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI69" s="48" t="inlineStr">
         <is>
@@ -16304,81 +16296,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK69" s="50" t="n">
+      <c r="AK69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AN69" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AP69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AQ69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR69" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS69" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT69" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU69" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AX69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AY69" s="50" t="n">
         <v>2</v>
-      </c>
-      <c r="AL69" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AN69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AQ69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT69" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AW69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AX69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AY69" s="50" t="n">
-        <v>1</v>
       </c>
       <c r="AZ69" s="51" t="n">
         <v>2</v>
       </c>
       <c r="BA69" s="44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB69" s="45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
@@ -17130,7 +17118,7 @@
     <row r="73">
       <c r="A73" s="46" t="inlineStr">
         <is>
-          <t>Rita Cecilia de la Hoz del Villar</t>
+          <t>Armando Jose Mercado Vega</t>
         </is>
       </c>
       <c r="B73" s="47" t="inlineStr">
@@ -17140,7 +17128,7 @@
       </c>
       <c r="C73" s="47" t="inlineStr">
         <is>
-          <t>59326410200</t>
+          <t>57824284000</t>
         </is>
       </c>
       <c r="D73" s="48" t="inlineStr">
@@ -17213,10 +17201,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R73" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S73" s="48" t="inlineStr">
         <is>
@@ -17238,15 +17224,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W73" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X73" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="Y73" s="48" t="inlineStr">
         <is>
@@ -17293,10 +17275,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AH73" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AI73" s="48" t="inlineStr">
         <is>
@@ -17308,21 +17288,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK73" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="AL73" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM73" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AN73" s="52" t="n">
-        <v>1</v>
+      <c r="AN73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AO73" s="48" t="inlineStr">
         <is>
@@ -17339,19 +17319,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AR73" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS73" s="51" t="n">
-        <v>4</v>
+      <c r="AR73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AT73" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AU73" s="52" t="n">
-        <v>1</v>
+      <c r="AU73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AV73" s="48" t="inlineStr">
         <is>
@@ -17368,23 +17354,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AY73" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ73" s="51" t="n">
-        <v>1</v>
+      <c r="AY73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="BA73" s="44" t="n">
         <v>2</v>
       </c>
       <c r="BB73" s="45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>Oriana Susana Martinez Palomino</t>
+          <t>Rita Cecilia de la Hoz del Villar</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
@@ -17394,7 +17384,7 @@
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>58620428800</t>
+          <t>59326410200</t>
         </is>
       </c>
       <c r="D74" s="35" t="inlineStr">
@@ -17482,8 +17472,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U74" s="20" t="n">
-        <v>1</v>
+      <c r="U74" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V74" s="37" t="inlineStr">
         <is>
@@ -17495,8 +17487,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X74" s="39" t="n">
-        <v>1</v>
+      <c r="X74" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y74" s="40" t="inlineStr">
         <is>
@@ -17513,91 +17507,95 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB74" s="25" t="n">
-        <v>1</v>
+      <c r="AB74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC74" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD74" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE74" s="57" t="n">
+      <c r="AD74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL74" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="AF74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL74" s="58" t="n">
+      <c r="AM74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AN74" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AP74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AQ74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR74" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS74" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="AM74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AN74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AQ74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR74" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS74" s="43" t="n">
-        <v>3</v>
-      </c>
       <c r="AT74" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AU74" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AU74" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="AV74" s="36" t="inlineStr">
         <is>
@@ -17614,27 +17612,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AY74" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ74" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AY74" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ74" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="BA74" s="44" t="n">
         <v>2</v>
       </c>
       <c r="BB74" s="45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="46" t="inlineStr">
         <is>
-          <t>Armando Jose Mercado Vega</t>
+          <t>Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="B75" s="47" t="inlineStr">
@@ -17644,7 +17638,7 @@
       </c>
       <c r="C75" s="47" t="inlineStr">
         <is>
-          <t>57824284000</t>
+          <t>58620428800</t>
         </is>
       </c>
       <c r="D75" s="48" t="inlineStr">
@@ -17717,8 +17711,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R75" s="49" t="n">
-        <v>1</v>
+      <c r="R75" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S75" s="48" t="inlineStr">
         <is>
@@ -17730,18 +17726,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U75" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V75" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W75" s="50" t="n">
-        <v>1</v>
+      <c r="W75" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X75" s="51" t="n">
         <v>1</v>
@@ -17761,25 +17757,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB75" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="AC75" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD75" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE75" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="AF75" s="48" t="inlineStr">
         <is>
@@ -17791,8 +17781,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AH75" s="59" t="n">
-        <v>1</v>
+      <c r="AH75" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI75" s="48" t="inlineStr">
         <is>
@@ -17804,21 +17796,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK75" s="50" t="n">
-        <v>1</v>
+      <c r="AK75" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AL75" s="51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM75" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AN75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AN75" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AO75" s="48" t="inlineStr">
         <is>
@@ -17835,15 +17827,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AR75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AR75" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS75" s="51" t="n">
+        <v>3</v>
       </c>
       <c r="AT75" s="48" t="inlineStr">
         <is>
@@ -17884,7 +17872,7 @@
         <v>2</v>
       </c>
       <c r="BB75" s="45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -20189,7 +20177,7 @@
         <v>9</v>
       </c>
       <c r="AT85" s="49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU85" s="52" t="n">
         <v>3</v>
@@ -20208,16 +20196,16 @@
         </is>
       </c>
       <c r="AY85" s="50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ85" s="51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA85" s="44" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BB85" s="45" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86">
@@ -22782,7 +22770,7 @@
         </is>
       </c>
       <c r="AS96" s="43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT96" s="36" t="inlineStr">
         <is>
@@ -22819,7 +22807,7 @@
         <v>0</v>
       </c>
       <c r="BB96" s="45" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97">
@@ -26242,7 +26230,7 @@
     <row r="13">
       <c r="A13" s="46" t="inlineStr">
         <is>
-          <t>Edisson Chavarro Mesa</t>
+          <t>Alberto Patiño Vanegas</t>
         </is>
       </c>
       <c r="B13" s="47" t="inlineStr">
@@ -26252,11 +26240,13 @@
       </c>
       <c r="C13" s="47" t="inlineStr">
         <is>
-          <t>57188841051</t>
-        </is>
-      </c>
-      <c r="D13" s="49" t="n">
-        <v>1</v>
+          <t>57190688459</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E13" s="48" t="inlineStr">
         <is>
@@ -26268,21 +26258,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G13" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="H13" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="50" t="n">
-        <v>1</v>
+      <c r="I13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J13" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="48" t="inlineStr">
         <is>
@@ -26294,8 +26284,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M13" s="59" t="n">
-        <v>1</v>
+      <c r="M13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N13" s="53" t="n">
         <v>1</v>
@@ -26306,10 +26298,10 @@
         </is>
       </c>
       <c r="P13" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R13" s="48" t="inlineStr">
         <is>
@@ -26326,8 +26318,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U13" s="53" t="n">
-        <v>1</v>
+      <c r="U13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V13" s="48" t="inlineStr">
         <is>
@@ -26339,8 +26333,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X13" s="51" t="n">
-        <v>1</v>
+      <c r="X13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y13" s="48" t="inlineStr">
         <is>
@@ -26352,13 +26348,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA13" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AB13" s="53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC13" s="48" t="inlineStr">
         <is>
@@ -26389,7 +26383,7 @@
         </is>
       </c>
       <c r="AI13" s="53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ13" s="48" t="inlineStr">
         <is>
@@ -26402,17 +26396,13 @@
         </is>
       </c>
       <c r="AL13" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AN13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AM13" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AO13" s="48" t="inlineStr">
         <is>
@@ -26420,20 +26410,18 @@
         </is>
       </c>
       <c r="AP13" s="53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ13" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AR13" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AR13" s="50" t="n">
+        <v>2</v>
       </c>
       <c r="AS13" s="51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AT13" s="48" t="inlineStr">
         <is>
@@ -26450,8 +26438,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AW13" s="53" t="n">
-        <v>3</v>
+      <c r="AW13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AX13" s="48" t="inlineStr">
         <is>
@@ -26463,20 +26453,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AZ13" s="51" t="n">
-        <v>3</v>
+      <c r="AZ13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="BA13" s="44" t="n">
         <v>3</v>
       </c>
       <c r="BB13" s="45" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>Alberto Patiño Vanegas</t>
+          <t>Jorge Luis Villalba Acevedo</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
@@ -26486,7 +26478,7 @@
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>57190688459</t>
+          <t>57918628600</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
@@ -26504,151 +26496,153 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R14" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W14" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="43" t="n">
+      <c r="Y14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB14" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD14" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG14" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH14" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI14" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P14" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y14" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z14" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA14" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD14" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE14" s="57" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG14" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH14" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI14" s="30" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ14" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK14" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK14" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="AL14" s="58" t="n">
         <v>3</v>
       </c>
-      <c r="AM14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN14" s="8" t="n">
-        <v>1</v>
+      <c r="AM14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AN14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AO14" s="35" t="inlineStr">
         <is>
@@ -26656,39 +26650,39 @@
         </is>
       </c>
       <c r="AP14" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ14" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AR14" s="42" t="n">
+      <c r="AR14" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS14" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AV14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW14" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="AS14" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AW14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="AX14" s="36" t="inlineStr">
         <is>
           <t>—</t>
@@ -26699,22 +26693,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AZ14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AZ14" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="BA14" s="44" t="n">
         <v>3</v>
       </c>
       <c r="BB14" s="45" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis Villalba Acevedo</t>
+          <t>Edisson Chavarro Mesa</t>
         </is>
       </c>
       <c r="B15" s="47" t="inlineStr">
@@ -26724,13 +26716,11 @@
       </c>
       <c r="C15" s="47" t="inlineStr">
         <is>
-          <t>57918628600</t>
-        </is>
-      </c>
-      <c r="D15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57188841051</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="E15" s="48" t="inlineStr">
         <is>
@@ -26752,15 +26742,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I15" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="K15" s="48" t="inlineStr">
         <is>
@@ -26772,38 +26758,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M15" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="O15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P15" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="51" t="n">
+        <v>3</v>
       </c>
       <c r="R15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S15" s="52" t="n">
-        <v>1</v>
+      <c r="S15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="T15" s="48" t="inlineStr">
         <is>
@@ -26818,14 +26798,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W15" s="50" t="n">
-        <v>1</v>
+      <c r="W15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X15" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y15" s="49" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Y15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z15" s="48" t="inlineStr">
         <is>
@@ -26838,18 +26822,20 @@
         </is>
       </c>
       <c r="AB15" s="53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD15" s="50" t="n">
-        <v>1</v>
+      <c r="AD15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AE15" s="51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF15" s="48" t="inlineStr">
         <is>
@@ -26867,7 +26853,7 @@
         </is>
       </c>
       <c r="AI15" s="53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ15" s="48" t="inlineStr">
         <is>
@@ -26880,7 +26866,7 @@
         </is>
       </c>
       <c r="AL15" s="51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM15" s="48" t="inlineStr">
         <is>
@@ -26898,57 +26884,57 @@
         </is>
       </c>
       <c r="AP15" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS15" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AV15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW15" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="AQ15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS15" s="51" t="n">
+      <c r="AX15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AY15" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ15" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="AT15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AW15" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AY15" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ15" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="BA15" s="44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB15" s="45" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -27182,10 +27168,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AW16" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AW16" s="15" t="n">
+        <v>2</v>
       </c>
       <c r="AX16" s="36" t="inlineStr">
         <is>
@@ -27197,16 +27181,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AZ16" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AZ16" s="55" t="n">
+        <v>2</v>
       </c>
       <c r="BA16" s="44" t="n">
         <v>2</v>
       </c>
       <c r="BB16" s="45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -30278,7 +30260,7 @@
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>Sonia Helena Contreras Ortiz</t>
+          <t>Mary Judith Arias Tapia</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
@@ -30288,11 +30270,13 @@
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>57210822856</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>1</v>
+          <t>57219403758</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E32" s="35" t="inlineStr">
         <is>
@@ -30304,30 +30288,38 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="10" t="n">
-        <v>6</v>
+      <c r="G32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H32" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" s="14" t="n">
-        <v>1</v>
+      <c r="I32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N32" s="36" t="inlineStr">
         <is>
@@ -30343,18 +30335,18 @@
         <v>1</v>
       </c>
       <c r="Q32" s="55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R32" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="S32" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T32" s="19" t="n">
-        <v>1</v>
+      <c r="S32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="U32" s="37" t="inlineStr">
         <is>
@@ -30370,10 +30362,12 @@
         <v>2</v>
       </c>
       <c r="X32" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Y32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z32" s="40" t="inlineStr">
         <is>
@@ -30385,24 +30379,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB32" s="25" t="n">
-        <v>4</v>
+      <c r="AB32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC32" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD32" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE32" s="57" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF32" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF32" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="AG32" s="41" t="inlineStr">
         <is>
@@ -30414,37 +30412,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI32" s="30" t="n">
-        <v>7</v>
+      <c r="AI32" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AJ32" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK32" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK32" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="AL32" s="58" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM32" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AM32" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="AN32" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AO32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP32" s="10" t="n">
-        <v>6</v>
+      <c r="AO32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AP32" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AQ32" s="35" t="inlineStr">
         <is>
@@ -30455,48 +30455,46 @@
         <v>1</v>
       </c>
       <c r="AS32" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT32" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU32" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" s="12" t="n">
         <v>2</v>
       </c>
+      <c r="AU32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW32" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="AX32" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AY32" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AY32" s="54" t="n">
+        <v>2</v>
       </c>
       <c r="AZ32" s="55" t="n">
         <v>3</v>
       </c>
       <c r="BA32" s="44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB32" s="45" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>Mary Judith Arias Tapia</t>
+          <t>Sonia Helena Contreras Ortiz</t>
         </is>
       </c>
       <c r="B33" s="47" t="inlineStr">
@@ -30506,13 +30504,11 @@
       </c>
       <c r="C33" s="47" t="inlineStr">
         <is>
-          <t>57219403758</t>
-        </is>
-      </c>
-      <c r="D33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>57210822856</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
@@ -30524,38 +30520,30 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G33" s="53" t="n">
+        <v>6</v>
       </c>
       <c r="H33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K33" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I33" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="N33" s="48" t="inlineStr">
         <is>
@@ -30571,18 +30559,18 @@
         <v>1</v>
       </c>
       <c r="Q33" s="51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R33" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="S33" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="T33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="S33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T33" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="U33" s="48" t="inlineStr">
         <is>
@@ -30598,89 +30586,81 @@
         <v>2</v>
       </c>
       <c r="X33" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB33" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD33" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI33" s="53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL33" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AN33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO33" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="Y33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF33" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK33" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM33" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AP33" s="53" t="n">
+        <v>6</v>
       </c>
       <c r="AQ33" s="48" t="inlineStr">
         <is>
@@ -30691,42 +30671,42 @@
         <v>1</v>
       </c>
       <c r="AS33" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT33" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AV33" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW33" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="AU33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AW33" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="AX33" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AY33" s="50" t="n">
-        <v>1</v>
+      <c r="AY33" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AZ33" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA33" s="44" t="n">
         <v>6</v>
       </c>
       <c r="BB33" s="45" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
@@ -37232,7 +37212,7 @@
         </is>
       </c>
       <c r="AW60" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX60" s="36" t="inlineStr">
         <is>
@@ -37240,16 +37220,16 @@
         </is>
       </c>
       <c r="AY60" s="54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ60" s="55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA60" s="44" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB60" s="45" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -37438,10 +37418,8 @@
       <c r="AU61" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="AV61" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AV61" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AW61" s="48" t="inlineStr">
         <is>
@@ -37454,16 +37432,16 @@
         </is>
       </c>
       <c r="AY61" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ61" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA61" s="44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB61" s="45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
@@ -37941,7 +37919,7 @@
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>Jorge Luis del Rio Cortina</t>
+          <t>Elias Rafael Geney Castro</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
@@ -37951,7 +37929,7 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>57197807415</t>
+          <t>57427876200</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -38004,25 +37982,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="N64" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="O64" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P64" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="R64" s="37" t="inlineStr">
         <is>
@@ -38069,13 +38041,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA64" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB64" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AA64" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB64" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="AC64" s="40" t="inlineStr">
         <is>
@@ -38103,87 +38075,93 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI64" s="30" t="n">
+      <c r="AI64" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ64" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK64" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL64" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AN64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AQ64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR64" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS64" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT64" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU64" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV64" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW64" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX64" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AY64" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="AJ64" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK64" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL64" s="58" t="n">
+      <c r="AZ64" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="AM64" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP64" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR64" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS64" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT64" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV64" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AX64" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AY64" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ64" s="55" t="n">
-        <v>3</v>
-      </c>
       <c r="BA64" s="44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB64" s="45" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="46" t="inlineStr">
         <is>
-          <t>Jorge Luis Alvis Arrieta</t>
+          <t>Jorge Luis del Rio Cortina</t>
         </is>
       </c>
       <c r="B65" s="47" t="inlineStr">
@@ -38193,7 +38171,7 @@
       </c>
       <c r="C65" s="47" t="inlineStr">
         <is>
-          <t>58068307100</t>
+          <t>57197807415</t>
         </is>
       </c>
       <c r="D65" s="48" t="inlineStr">
@@ -38236,8 +38214,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L65" s="52" t="n">
-        <v>1</v>
+      <c r="L65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M65" s="48" t="inlineStr">
         <is>
@@ -38254,11 +38234,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P65" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="51" t="n">
-        <v>1</v>
+      <c r="P65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R65" s="48" t="inlineStr">
         <is>
@@ -38340,66 +38324,58 @@
         </is>
       </c>
       <c r="AI65" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL65" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM65" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="AJ65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK65" s="50" t="n">
+      <c r="AN65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AP65" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ65" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR65" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="AL65" s="51" t="n">
+      <c r="AS65" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT65" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="AM65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AN65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AQ65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT65" s="49" t="n">
-        <v>1</v>
-      </c>
       <c r="AU65" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AV65" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AV65" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="AW65" s="48" t="inlineStr">
         <is>
@@ -38412,22 +38388,22 @@
         </is>
       </c>
       <c r="AY65" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ65" s="51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA65" s="44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB65" s="45" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>Elias Rafael Geney Castro</t>
+          <t>Jorge Luis Alvis Arrieta</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
@@ -38437,7 +38413,7 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>57427876200</t>
+          <t>58068307100</t>
         </is>
       </c>
       <c r="D66" s="35" t="inlineStr">
@@ -38480,18 +38456,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L66" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L66" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="M66" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N66" s="15" t="n">
-        <v>1</v>
+      <c r="N66" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O66" s="36" t="inlineStr">
         <is>
@@ -38549,13 +38525,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AA66" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB66" s="25" t="n">
-        <v>1</v>
+      <c r="AA66" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AC66" s="40" t="inlineStr">
         <is>
@@ -38583,25 +38559,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AI66" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AI66" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="AJ66" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK66" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL66" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK66" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL66" s="58" t="n">
+        <v>2</v>
       </c>
       <c r="AM66" s="35" t="inlineStr">
         <is>
@@ -38613,8 +38583,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AO66" s="9" t="n">
-        <v>1</v>
+      <c r="AO66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AP66" s="35" t="inlineStr">
         <is>
@@ -38626,27 +38598,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AR66" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS66" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT66" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU66" s="13" t="n">
-        <v>1</v>
+      <c r="AR66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT66" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU66" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AV66" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AW66" s="15" t="n">
-        <v>1</v>
+      <c r="AW66" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AX66" s="36" t="inlineStr">
         <is>
@@ -38654,10 +38632,10 @@
         </is>
       </c>
       <c r="AY66" s="54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ66" s="55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA66" s="44" t="n">
         <v>5</v>
@@ -38913,7 +38891,7 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>Tania Isabel Jimenez Castilla</t>
+          <t>David Javier Fortich Perez</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
@@ -38923,7 +38901,7 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>57204842254</t>
+          <t>57201036449</t>
         </is>
       </c>
       <c r="D68" s="35" t="inlineStr">
@@ -38941,8 +38919,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G68" s="10" t="n">
-        <v>1</v>
+      <c r="G68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H68" s="35" t="inlineStr">
         <is>
@@ -38954,150 +38934,152 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J68" s="43" t="n">
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X68" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE68" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF68" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG68" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI68" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ68" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK68" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="K68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R68" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V68" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W68" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="X68" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE68" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL68" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AL68" s="58" t="n">
+        <v>2</v>
       </c>
       <c r="AM68" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AN68" s="8" t="n">
-        <v>1</v>
+      <c r="AN68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AO68" s="35" t="inlineStr">
         <is>
@@ -39114,11 +39096,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AR68" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS68" s="43" t="n">
-        <v>1</v>
+      <c r="AR68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AT68" s="12" t="n">
         <v>2</v>
@@ -39133,10 +39119,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AW68" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AW68" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="AX68" s="36" t="inlineStr">
         <is>
@@ -39147,19 +39131,19 @@
         <v>2</v>
       </c>
       <c r="AZ68" s="55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA68" s="44" t="n">
         <v>4</v>
       </c>
       <c r="BB68" s="45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="46" t="inlineStr">
         <is>
-          <t>David Javier Fortich Perez</t>
+          <t>Tania Isabel Jimenez Castilla</t>
         </is>
       </c>
       <c r="B69" s="47" t="inlineStr">
@@ -39169,7 +39153,7 @@
       </c>
       <c r="C69" s="47" t="inlineStr">
         <is>
-          <t>57201036449</t>
+          <t>57204842254</t>
         </is>
       </c>
       <c r="D69" s="48" t="inlineStr">
@@ -39187,10 +39171,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G69" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="H69" s="48" t="inlineStr">
         <is>
@@ -39202,10 +39184,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="K69" s="48" t="inlineStr">
         <is>
@@ -39242,10 +39222,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R69" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S69" s="48" t="inlineStr">
         <is>
@@ -39267,15 +39245,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W69" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X69" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="Y69" s="48" t="inlineStr">
         <is>
@@ -39317,11 +39291,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AG69" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH69" s="59" t="n">
-        <v>1</v>
+      <c r="AG69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AI69" s="48" t="inlineStr">
         <is>
@@ -39333,21 +39311,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK69" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL69" s="51" t="n">
-        <v>2</v>
+      <c r="AK69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL69" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AM69" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AN69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AN69" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="AO69" s="48" t="inlineStr">
         <is>
@@ -39364,15 +39344,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AR69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS69" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AR69" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS69" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="AT69" s="49" t="n">
         <v>2</v>
@@ -39398,16 +39374,16 @@
         </is>
       </c>
       <c r="AY69" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ69" s="51" t="n">
         <v>2</v>
       </c>
       <c r="BA69" s="44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB69" s="45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
@@ -40153,7 +40129,7 @@
     <row r="73">
       <c r="A73" s="46" t="inlineStr">
         <is>
-          <t>Rita Cecilia de la Hoz del Villar</t>
+          <t>Armando Jose Mercado Vega</t>
         </is>
       </c>
       <c r="B73" s="47" t="inlineStr">
@@ -40163,7 +40139,7 @@
       </c>
       <c r="C73" s="47" t="inlineStr">
         <is>
-          <t>59326410200</t>
+          <t>57824284000</t>
         </is>
       </c>
       <c r="D73" s="48" t="inlineStr">
@@ -40236,10 +40212,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R73" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="S73" s="48" t="inlineStr">
         <is>
@@ -40261,15 +40235,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="W73" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X73" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="Y73" s="48" t="inlineStr">
         <is>
@@ -40322,23 +40292,23 @@
         </is>
       </c>
       <c r="AI73" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ73" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK73" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AK73" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="AL73" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM73" s="49" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AM73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AN73" s="48" t="inlineStr">
         <is>
@@ -40350,22 +40320,30 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AP73" s="53" t="n">
-        <v>1</v>
+      <c r="AP73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AQ73" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AR73" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS73" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT73" s="49" t="n">
-        <v>1</v>
+      <c r="AR73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AU73" s="48" t="inlineStr">
         <is>
@@ -40387,23 +40365,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AY73" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ73" s="51" t="n">
-        <v>1</v>
+      <c r="AY73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AZ73" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="BA73" s="44" t="n">
         <v>2</v>
       </c>
       <c r="BB73" s="45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>Oriana Susana Martinez Palomino</t>
+          <t>Rita Cecilia de la Hoz del Villar</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
@@ -40413,7 +40395,7 @@
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>58620428800</t>
+          <t>59326410200</t>
         </is>
       </c>
       <c r="D74" s="35" t="inlineStr">
@@ -40501,8 +40483,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U74" s="20" t="n">
-        <v>1</v>
+      <c r="U74" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V74" s="37" t="inlineStr">
         <is>
@@ -40514,8 +40498,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="X74" s="39" t="n">
-        <v>1</v>
+      <c r="X74" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Y74" s="40" t="inlineStr">
         <is>
@@ -40532,82 +40518,86 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB74" s="25" t="n">
+      <c r="AB74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI74" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="AC74" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD74" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE74" s="57" t="n">
+      <c r="AJ74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK74" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AL74" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="AF74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI74" s="30" t="n">
+      <c r="AM74" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AP74" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR74" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS74" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="AJ74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL74" s="58" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AP74" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AR74" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS74" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT74" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AT74" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="AU74" s="36" t="inlineStr">
         <is>
@@ -40629,27 +40619,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AY74" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AZ74" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AY74" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ74" s="55" t="n">
+        <v>1</v>
       </c>
       <c r="BA74" s="44" t="n">
         <v>2</v>
       </c>
       <c r="BB74" s="45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="46" t="inlineStr">
         <is>
-          <t>Armando Jose Mercado Vega</t>
+          <t>Oriana Susana Martinez Palomino</t>
         </is>
       </c>
       <c r="B75" s="47" t="inlineStr">
@@ -40659,7 +40645,7 @@
       </c>
       <c r="C75" s="47" t="inlineStr">
         <is>
-          <t>57824284000</t>
+          <t>58620428800</t>
         </is>
       </c>
       <c r="D75" s="48" t="inlineStr">
@@ -40732,8 +40718,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R75" s="49" t="n">
-        <v>1</v>
+      <c r="R75" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="S75" s="48" t="inlineStr">
         <is>
@@ -40745,18 +40733,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="U75" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="V75" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W75" s="50" t="n">
-        <v>1</v>
+      <c r="W75" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="X75" s="51" t="n">
         <v>1</v>
@@ -40776,25 +40764,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AB75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AB75" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="AC75" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AD75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AD75" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE75" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="AF75" s="48" t="inlineStr">
         <is>
@@ -40812,23 +40794,23 @@
         </is>
       </c>
       <c r="AI75" s="53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ75" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AK75" s="50" t="n">
-        <v>1</v>
+      <c r="AK75" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AL75" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="AM75" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="AN75" s="48" t="inlineStr">
         <is>
@@ -40840,25 +40822,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AP75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AP75" s="53" t="n">
+        <v>2</v>
       </c>
       <c r="AQ75" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AR75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS75" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AR75" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS75" s="51" t="n">
+        <v>3</v>
       </c>
       <c r="AT75" s="48" t="inlineStr">
         <is>
@@ -40899,7 +40875,7 @@
         <v>2</v>
       </c>
       <c r="BB75" s="45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -43184,7 +43160,7 @@
         <v>9</v>
       </c>
       <c r="AT85" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU85" s="52" t="n">
         <v>9</v>
@@ -43203,16 +43179,16 @@
         </is>
       </c>
       <c r="AY85" s="50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ85" s="51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA85" s="44" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BB85" s="45" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86">
@@ -45726,7 +45702,7 @@
         <v>1</v>
       </c>
       <c r="AP96" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ96" s="35" t="inlineStr">
         <is>
@@ -45739,7 +45715,7 @@
         </is>
       </c>
       <c r="AS96" s="43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT96" s="36" t="inlineStr">
         <is>
@@ -45774,7 +45750,7 @@
         <v>0</v>
       </c>
       <c r="BB96" s="45" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97">
